--- a/output/full_scan/batch_seq1_2026-09-21.xlsx
+++ b/output/full_scan/batch_seq1_2026-09-21.xlsx
@@ -4407,7 +4407,7 @@
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>239.9810759093122</v>
+        <v>239.9810759093121</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>80.3</v>
